--- a/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt2_rubricas.xlsx
@@ -1932,13 +1932,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBB5D6D5-AD70-432B-B57C-13096B01477D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03EE9E5C-AAB3-424E-ADA5-8C4321329974}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4D08463-FCAC-416A-9B09-B77982D62801}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F39E921-CC56-4852-A1DF-98BAA37FC341}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E84CEFBB-D3A1-4039-917A-38CE163C753B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C54E8E1-6466-4001-8A87-72B372A91B2C}"/>
 </file>